--- a/data/trans_orig/IP1012-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149858</t>
+          <t>149677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288653</t>
+          <t>288598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191281</t>
+          <t>191308</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402827</t>
+          <t>402838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145787</t>
+          <t>146444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284149</t>
+          <t>283859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205642</t>
+          <t>205635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198338</t>
+          <t>198978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206304</t>
+          <t>206273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407109</t>
+          <t>407184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>414984</t>
+          <t>414979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>675700</t>
+          <t>675622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>680392</t>
+          <t>680386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711942</t>
+          <t>711744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720101</t>
+          <t>720083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1389522</t>
+          <t>1390145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1399628</t>
+          <t>1399743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130041</t>
+          <t>129695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147432</t>
+          <t>147268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>153230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>280386</t>
+          <t>281040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288685</t>
+          <t>288751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201718</t>
+          <t>202754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423877</t>
+          <t>424079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159001</t>
+          <t>159699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313700</t>
+          <t>314677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206884</t>
+          <t>206039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202265</t>
+          <t>203343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411827</t>
+          <t>412080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416766</t>
+          <t>416764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>699257</t>
+          <t>698681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>706010</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>737279</t>
+          <t>737697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746262</t>
+          <t>746164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1439472</t>
+          <t>1440256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1450822</t>
+          <t>1450871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220646</t>
+          <t>221235</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428491</t>
+          <t>428290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162848</t>
+          <t>163174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318077</t>
+          <t>318844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201101</t>
+          <t>201532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408393</t>
+          <t>408527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>738470</t>
+          <t>738013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744135</t>
+          <t>744121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1442369</t>
+          <t>1442258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448501</t>
+          <t>1448505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1012-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152404</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148808</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152404</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149677</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>428</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288598</t>
+          <t>288098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1276</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3855</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4078</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4467</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>193887</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191308</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191313</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>632</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402838</t>
+          <t>403227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3615</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149015</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146033</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149015</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>146444</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>460</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283859</t>
+          <t>284254</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4374</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3680</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4374</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8846</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>203450</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198305</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206253</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>208582</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>205635</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>205215</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>203450</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>198978</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206273</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>573</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407184</t>
+          <t>407130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>414979</t>
+          <t>414965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10822</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5399</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5643</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2617</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10956</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1078</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>717011</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>711878</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720202</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679012</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675622</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680386</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>675378</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680387</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>717011</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>711744</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>720083</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2093</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1390145</t>
+          <t>1390657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1399743</t>
+          <t>1399781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6375</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1841</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6696</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5574</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2780</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6637</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>151125</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>147530</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153216</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>134550</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>129695</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130817</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,65%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>151125</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>147268</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153230</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>389</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281040</t>
+          <t>280623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288751</t>
+          <t>288553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153905</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153905</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153905</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153905</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153905</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204742</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>202754</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>202101</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>637</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>424079</t>
+          <t>424467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,92 +3355,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7185</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2049</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6286</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163936</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158800</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>163936</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>159699</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>494</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314677</t>
+          <t>314662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>746</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4261</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4461</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3739</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205839</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202705</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209554</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>206039</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>205839</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205839</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203343</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>553</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412080</t>
+          <t>411083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416764</t>
+          <t>416761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11838</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3243</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8247</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,13%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11252</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742877</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>737111</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>746228</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703685</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698681</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>706006</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>699189</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>706005</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,87%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742877</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>737697</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>746164</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2073</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1440256</t>
+          <t>1439551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1450871</t>
+          <t>1450743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>618</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3124</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3096</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>223741</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>221218</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>223741</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>221235</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>665</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428290</t>
+          <t>428510</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4384</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3499</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3826</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162289</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>163174</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>506</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318844</t>
+          <t>318875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4911</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1359</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4204</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4706</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204377</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>200825</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204377</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201532</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>568</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408527</t>
+          <t>408450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,92 +5988,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6647</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2736</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6831</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742108</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738197</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744133</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742108</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>738013</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744121</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2121</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1442258</t>
+          <t>1442525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448505</t>
+          <t>1448503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
